--- a/pacjenci/BARBARA KWARCINSKA.xlsx
+++ b/pacjenci/BARBARA KWARCINSKA.xlsx
@@ -483,7 +483,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Aktywna choroba</t>
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Aktywna choroba</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -603,7 +615,11 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -643,7 +659,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/BARBARA KWARCINSKA.xlsx
+++ b/pacjenci/BARBARA KWARCINSKA.xlsx
@@ -413,323 +413,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>17.01.2023</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 112 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne szyi po stronie prawej grup: - 2A wielkości do 25x21 mm SUV max do 9,3; - 2B wielkości do 12 mm SUV max do 8,7; - 3 wielkości wielkości do 17x12 mm SUV max do 8,0; - 4 wielkości 29x27x55 mm SUV max do 9,4; - 5B wielkości 24x10 mm SUV max do 4,0. Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 6,7- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych..  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne we wnęce płuca lewego, wielkości do 14x10 mm wg PET SUV max 4,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - w miednicy przedkrzyżowo wielkości do 11x18 mm, SUV max do 7,5; - pachwinowe prawe, wielkości do 23x15 mm, SUV max do 12,6. Wzmożony metabolizm FDG w zakresie krzywizny mniejszej żołądka SUV max 3,9 oraz w części odźwiernikowej SUV max 5,4- do kontroli endoskopowej. Ogniskowo wzmożony metabolizm FDG w grzbietowej części trzonu macicy [Im fuz. 220], SUV max 4,4-do kontroli w badaniu TK/MR z kontrastem dożylnym. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,3 - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych po stronie prawej SUV max 3,7- zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>12.6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>11.05.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena odpowiedzi po 3 cyklach cht.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 113 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne szyi po stronie prawej grupy 2A wielkości do 10x9 mm SUV max 4,0; Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych..  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Wzmożony metabolizm FDG w żołądku oraz w jelitach, SUV max do 5,7- do kontroli endoskopowej. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?   Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,9.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych na szyi grupy 2A. W porównaniu do badania poprzedniego PET/CT - częściowa odpowiedź metaboliczna choroby chłoniakowej na stosowane leczenie.    8.08.2023 Zakres badania:  od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 116 mg%. Problem kliniczny: Chłoniak nieziarniczy rozlany. Ocena remisji choroby.  Konsultujący specjalista radiologii i diagnostyki obrazowej: Dr n. med. Agata Brzozowska-Czarnek  Głowa i szyja: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUV max 7,1 - do rozważenia kontrola endoskopowa. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe obustronnie, wielkości do ok. 14x11mm.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,8 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.   Wartości referencyjne: MBPS SUVmax 2,9; Prawy płat wątroby SUVmax do 3,9.  Wnioski: Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej. Uwidoczniono rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka - do rozważenia kontrola endoskopowa.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>7.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>23.03.2024</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Podejrzenie wznowy.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 125 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Symetrycznie wzmozona aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUVmax 12,7. Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne grup: - po stronie prawej: 1B, 2, 3, 4, wielkości wg PET do 28x51mm, SUVmax 11,3; - po stronie lewej 1B, 2, 3, 4, wielkości wg PET do 22x16mm, SUVmax 7,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUVmax 6,3 - do rozważenia kontrola endoskopowa. Aktywne metabolicznie węzły chłonne biodrowe zewnętrzne, udowe i pachwinowe prawe wielkości wg PET do 29x11mm, SUV max 7,8. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22mm - zmiana w śledzionie? w przyleganiu do śledziony? - do oceny w badaniu TK/MR jamy brzusznej, z kontrastem dożylnym. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,5 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.   Wartości referencyjne: MBPS SUVmax 2,5; Prawy płat wątroby SUVmax do 4,9.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony - progresja choroby.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>12.7</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>17.04.2024</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena odpowiedzi na leczenie.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 64 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Asymetrycznie zwiększony metabolizm FDG w prawym płacie skroniowym, SUVmax 12,7 oraz lewym płacie potylicznym, SUVmax 13,2 - obraz niejednoznaczny - do oceny w badaniu MR głowy z kontrastem dożylnym. Symetrycznie wzmożona aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUVmax do 5,1. Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne  po stronie prawej grup 1B, 2, 3, 4, wielkości wg PET do 28x41mm, SUVmax 12,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym oraz nieco w worku osierdziowym od strony PK. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUVmax 6,4 - do rozważenia kontrola endoskopowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Niejednorodnie wzmożony metabolizm FDG w układzie kostnym - związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.   Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 4,2.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej (ilość zmian na szyi po stronie prawej porównywalna do badania poprzedniego PET z 26.03.2024).</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>13.2</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>25.06.2024</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena aktualnego stanu po leczeniu.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>całe ciało Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 106 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości 25x42x55 mm SUVmax 14,0. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 6 średnicy 10 mm SUV max  8,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w części odźwiernikowej żołądka, SUV max do 7,6 - odczynowo?. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0- w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywny metabolicznie węzeł chłonny w dolnej części uda prawego średnicy 9 mm SUV max 13,4 [Im fuz. 223]. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na długości 77 mm wg PET SUV max 11,0 - do oceny w badaniu Angio-TK. Żylaki kończyn dolnych, więcej po stronie lewej.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 4,3.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych po obu stronach przepony. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego - do oceny w badaniu Angio-TK. W porównaniu do poprzedniego badania PET/CT z dnia 17.04.2024 - częściowa regresja metaboliczna i radiologiczna zmian w obrębie szyi po stronie prawej, natomiast standardowy zakres poprzedniego badania nie pozwala na porównanie zmian w dystalnej części uda prawego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>14</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>23.07.2024</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>DLBCL - wznowa. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>całe ciało Akwizycję przeprowadzono  po 65min od podania 18F-FDG. Glikemia: 97mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości wg PET 54x38x68 mm SUVmax 15,4. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 4/guzek płata prawego tarczycy, średnicy wg PET 15mm SUV max  7,4 - do oceny w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Aktywny metabolicznie węzeł chłonny pachwinowy prawy średnicy wg PET 10mm, SUV max 3,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do górnego bieguna śledziony nadal widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Poza powyższym - dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0 - w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywne metabolicznie węzły chłonne w dolnej części uda prawego oraz w okolicy kolana, średnicy wg PET do 15 mm SUV max 15,3. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na łącznej długości wg PET  241mm, SUV max 19,6. Żylaki kończyn dolnych, więcej po stronie lewej.  Wartości referencyjne: MBPS SUVmax 3,0; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem węzłów chłonnych po obu stronach przepony. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego  W porównaniu do poprzedniego badania PET/CT z dnia 25.06.2024 - progresja wielkości nacieku w grzbietowo-dolnej części uda prawego.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>19.6</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/BARBARA KWARCINSKA.xlsx
+++ b/pacjenci/BARBARA KWARCINSKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 112 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne szyi po stronie prawej grup: - 2A wielkości do 25x21 mm SUV max do 9,3; - 2B wielkości do 12 mm SUV max do 8,7; - 3 wielkości wielkości do 17x12 mm SUV max do 8,0; - 4 wielkości 29x27x55 mm SUV max do 9,4; - 5B wielkości 24x10 mm SUV max do 4,0. Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 6,7- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych..  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne we wnęce płuca lewego, wielkości do 14x10 mm wg PET SUV max 4,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - w miednicy przedkrzyżowo wielkości do 11x18 mm, SUV max do 7,5; - pachwinowe prawe, wielkości do 23x15 mm, SUV max do 12,6. Wzmożony metabolizm FDG w zakresie krzywizny mniejszej żołądka SUV max 3,9 oraz w części odźwiernikowej SUV max 5,4- do kontroli endoskopowej. Ogniskowo wzmożony metabolizm FDG w grzbietowej części trzonu macicy [Im fuz. 220], SUV max 4,4-do kontroli w badaniu TK/MR z kontrastem dożylnym. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,3 - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych po stronie prawej SUV max 3,7- zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne szyi po stronie prawej grup: - 2A wielkości do 25x21 mm SUV max do 9,3; - 2B wielkości do 12 mm SUV max do 8,7; - 3 wielkości wielkości do 17x12 mm SUV max do 8,0; - 4 wielkości 29x27x55 mm SUV max do 9,4; - 5B wielkości 24x10 mm SUV max do 4,0. Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 6,7- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych..</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne we wnęce płuca lewego, wielkości do 14x10 mm wg PET SUV max 4,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - w miednicy przedkrzyżowo wielkości do 11x18 mm, SUV max do 7,5; - pachwinowe prawe, wielkości do 23x15 mm, SUV max do 12,6. Wzmożony metabolizm FDG w zakresie krzywizny mniejszej żołądka SUV max 3,9 oraz w części odźwiernikowej SUV max 5,4- do kontroli endoskopowej. Ogniskowo wzmożony metabolizm FDG w grzbietowej części trzonu macicy [Im fuz. 220], SUV max 4,4-do kontroli w badaniu TK/MR z kontrastem dożylnym. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,3 - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych po stronie prawej SUV max 3,7- zmiany odczynowo-przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 113 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne szyi po stronie prawej grupy 2A wielkości do 10x9 mm SUV max 4,0; Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych..  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Wzmożony metabolizm FDG w żołądku oraz w jelitach, SUV max do 5,7- do kontroli endoskopowej. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?   Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,9.</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne szyi po stronie prawej grupy 2A wielkości do 10x9 mm SUV max 4,0; Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych..</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w żołądku oraz w jelitach, SUV max do 5,7- do kontroli endoskopowej. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych na szyi grupy 2A. W porównaniu do badania poprzedniego PET/CT - częściowa odpowiedź metaboliczna choroby chłoniakowej na stosowane leczenie.    8.08.2023 Zakres badania:  od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 116 mg%. Problem kliniczny: Chłoniak nieziarniczy rozlany. Ocena remisji choroby.  Konsultujący specjalista radiologii i diagnostyki obrazowej: Dr n. med. Agata Brzozowska-Czarnek  Głowa i szyja: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUV max 7,1 - do rozważenia kontrola endoskopowa. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe obustronnie, wielkości do ok. 14x11mm.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,8 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.   Wartości referencyjne: MBPS SUVmax 2,9; Prawy płat wątroby SUVmax do 3,9.  Wnioski: Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej. Uwidoczniono rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka - do rozważenia kontrola endoskopowa.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 125 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmozona aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUVmax 12,7. Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne grup: - po stronie prawej: 1B, 2, 3, 4, wielkości wg PET do 28x51mm, SUVmax 11,3; - po stronie lewej 1B, 2, 3, 4, wielkości wg PET do 22x16mm, SUVmax 7,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUVmax 6,3 - do rozważenia kontrola endoskopowa. Aktywne metabolicznie węzły chłonne biodrowe zewnętrzne, udowe i pachwinowe prawe wielkości wg PET do 29x11mm, SUV max 7,8. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22mm - zmiana w śledzionie? w przyleganiu do śledziony? - do oceny w badaniu TK/MR jamy brzusznej, z kontrastem dożylnym. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,5 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.   Wartości referencyjne: MBPS SUVmax 2,5; Prawy płat wątroby SUVmax do 4,9.</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmozona aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUVmax 12,7. Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne grup: - po stronie prawej: 1B, 2, 3, 4, wielkości wg PET do 28x51mm, SUVmax 11,3; - po stronie lewej 1B, 2, 3, 4, wielkości wg PET do 22x16mm, SUVmax 7,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUVmax 6,3 - do rozważenia kontrola endoskopowa. Aktywne metabolicznie węzły chłonne biodrowe zewnętrzne, udowe i pachwinowe prawe wielkości wg PET do 29x11mm, SUV max 7,8. Pobudzenie metaboliczne w nadnerczu lewym SUV max 3,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22mm - zmiana w śledzionie? w przyleganiu do śledziony? - do oceny w badaniu TK/MR jamy brzusznej, z kontrastem dożylnym. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,5 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony - progresja choroby.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>12.7</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 64 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Asymetrycznie zwiększony metabolizm FDG w prawym płacie skroniowym, SUVmax 12,7 oraz lewym płacie potylicznym, SUVmax 13,2 - obraz niejednoznaczny - do oceny w badaniu MR głowy z kontrastem dożylnym. Symetrycznie wzmożona aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUVmax do 5,1. Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne  po stronie prawej grup 1B, 2, 3, 4, wielkości wg PET do 28x41mm, SUVmax 12,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym oraz nieco w worku osierdziowym od strony PK. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUVmax 6,4 - do rozważenia kontrola endoskopowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Niejednorodnie wzmożony metabolizm FDG w układzie kostnym - związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.   Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 4,2.</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Asymetrycznie zwiększony metabolizm FDG w prawym płacie skroniowym, SUVmax 12,7 oraz lewym płacie potylicznym, SUVmax 13,2 - obraz niejednoznaczny - do oceny w badaniu MR głowy z kontrastem dożylnym. Symetrycznie wzmożona aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUVmax do 5,1. Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne  po stronie prawej grup 1B, 2, 3, 4, wielkości wg PET do 28x41mm, SUVmax 12,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w zachyłku przeponowo-sercowym prawym oraz nieco w worku osierdziowym od strony PK. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, najbardziej nasilone przykręgosłupowo po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w odźwiernikowej i przedodźwiernikowej części żołądka, SUVmax 6,4 - do rozważenia kontrola endoskopowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Niejednorodnie wzmożony metabolizm FDG w układzie kostnym - związany ze stosowanym leczeniem?. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Rozlanie zwiększony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej (ilość zmian na szyi po stronie prawej porównywalna do badania poprzedniego PET z 26.03.2024).</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>całe ciało Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 106 mg%.</t>
+          <t>całe ciało</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości 25x42x55 mm SUVmax 14,0. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 6 średnicy 10 mm SUV max  8,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w części odźwiernikowej żołądka, SUV max do 7,6 - odczynowo?. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0- w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywny metabolicznie węzeł chłonny w dolnej części uda prawego średnicy 9 mm SUV max 13,4 [Im fuz. 223]. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na długości 77 mm wg PET SUV max 11,0 - do oceny w badaniu Angio-TK. Żylaki kończyn dolnych, więcej po stronie lewej.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 4,3.</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości 25x42x55 mm SUVmax 14,0. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 6 średnicy 10 mm SUV max  8,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w części odźwiernikowej żołądka, SUV max do 7,6 - odczynowo?. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do przedniego bieguna śledziony widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0- w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywny metabolicznie węzeł chłonny w dolnej części uda prawego średnicy 9 mm SUV max 13,4 [Im fuz. 223]. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na długości 77 mm wg PET SUV max 11,0 - do oceny w badaniu Angio-TK. Żylaki kończyn dolnych, więcej po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych po obu stronach przepony. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego - do oceny w badaniu Angio-TK. W porównaniu do poprzedniego badania PET/CT z dnia 17.04.2024 - częściowa regresja metaboliczna i radiologiczna zmian w obrębie szyi po stronie prawej, natomiast standardowy zakres poprzedniego badania nie pozwala na porównanie zmian w dystalnej części uda prawego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>całe ciało Akwizycję przeprowadzono  po 65min od podania 18F-FDG. Glikemia: 97mg%.</t>
+          <t>całe ciało</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości wg PET 54x38x68 mm SUVmax 15,4. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 4/guzek płata prawego tarczycy, średnicy wg PET 15mm SUV max  7,4 - do oceny w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Aktywny metabolicznie węzeł chłonny pachwinowy prawy średnicy wg PET 10mm, SUV max 3,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do górnego bieguna śledziony nadal widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Poza powyższym - dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0 - w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywne metabolicznie węzły chłonne w dolnej części uda prawego oraz w okolicy kolana, średnicy wg PET do 15 mm SUV max 15,3. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na łącznej długości wg PET  241mm, SUV max 19,6. Żylaki kończyn dolnych, więcej po stronie lewej.  Wartości referencyjne: MBPS SUVmax 3,0; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości wg PET 54x38x68 mm SUVmax 15,4. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 4/guzek płata prawego tarczycy, średnicy wg PET 15mm SUV max  7,4 - do oceny w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Aktywny metabolicznie węzeł chłonny pachwinowy prawy średnicy wg PET 10mm, SUV max 3,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do górnego bieguna śledziony nadal widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Poza powyższym - dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0 - w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywne metabolicznie węzły chłonne w dolnej części uda prawego oraz w okolicy kolana, średnicy wg PET do 15 mm SUV max 15,3. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na łącznej długości wg PET  241mm, SUV max 19,6. Żylaki kończyn dolnych, więcej po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem węzłów chłonnych po obu stronach przepony. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego  W porównaniu do poprzedniego badania PET/CT z dnia 25.06.2024 - progresja wielkości nacieku w grzbietowo-dolnej części uda prawego.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>19.6</v>
       </c>
     </row>
